--- a/artfynd/A 80-2025 artfynd.xlsx
+++ b/artfynd/A 80-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>133355233</v>
       </c>
       <c r="B2" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>133355234</v>
       </c>
       <c r="B3" t="n">
-        <v>84166</v>
+        <v>84167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>133210685</v>
       </c>
       <c r="B5" t="n">
-        <v>80342</v>
+        <v>80343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,6 +1081,124 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133799243</v>
+      </c>
+      <c r="B6" t="n">
+        <v>84167</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Längs Stig Norr om Mariebäck NR, Mariebäcksnäset, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>704292</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7101077</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Brant sluttning ovan skogsstig</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ernie Haglund</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ernie Haglund, Jörgen Sjögren, Albin Larsson Ekström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 80-2025 artfynd.xlsx
+++ b/artfynd/A 80-2025 artfynd.xlsx
@@ -1087,7 +1087,7 @@
         <v>133799243</v>
       </c>
       <c r="B6" t="n">
-        <v>84167</v>
+        <v>84169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 80-2025 artfynd.xlsx
+++ b/artfynd/A 80-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133355233</v>
       </c>
       <c r="B2" t="n">
-        <v>91940</v>
+        <v>91948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>133355234</v>
       </c>
       <c r="B3" t="n">
-        <v>84167</v>
+        <v>84170</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>133799243</v>
       </c>
       <c r="B6" t="n">
-        <v>84169</v>
+        <v>84170</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 80-2025 artfynd.xlsx
+++ b/artfynd/A 80-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133355233</v>
       </c>
       <c r="B2" t="n">
-        <v>91948</v>
+        <v>91967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>133355234</v>
       </c>
       <c r="B3" t="n">
-        <v>84170</v>
+        <v>84184</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>133210683</v>
       </c>
       <c r="B4" t="n">
-        <v>58332</v>
+        <v>58339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>133210685</v>
       </c>
       <c r="B5" t="n">
-        <v>80343</v>
+        <v>80357</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>133799243</v>
       </c>
       <c r="B6" t="n">
-        <v>84170</v>
+        <v>84184</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 80-2025 artfynd.xlsx
+++ b/artfynd/A 80-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133355233</v>
       </c>
       <c r="B2" t="n">
-        <v>91967</v>
+        <v>91977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>133355234</v>
       </c>
       <c r="B3" t="n">
-        <v>84184</v>
+        <v>84194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>133210683</v>
       </c>
       <c r="B4" t="n">
-        <v>58339</v>
+        <v>58349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>133210685</v>
       </c>
       <c r="B5" t="n">
-        <v>80357</v>
+        <v>80367</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>133799243</v>
       </c>
       <c r="B6" t="n">
-        <v>84184</v>
+        <v>84194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 80-2025 artfynd.xlsx
+++ b/artfynd/A 80-2025 artfynd.xlsx
@@ -1087,7 +1087,7 @@
         <v>133799243</v>
       </c>
       <c r="B6" t="n">
-        <v>84194</v>
+        <v>84195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 80-2025 artfynd.xlsx
+++ b/artfynd/A 80-2025 artfynd.xlsx
@@ -1087,7 +1087,7 @@
         <v>133799243</v>
       </c>
       <c r="B6" t="n">
-        <v>84195</v>
+        <v>84202</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 80-2025 artfynd.xlsx
+++ b/artfynd/A 80-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,41 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133355233</v>
+        <v>133355234</v>
       </c>
       <c r="B2" t="n">
-        <v>91977</v>
+        <v>84209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mariebäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>703923</v>
+        <v>704260</v>
       </c>
       <c r="R2" t="n">
-        <v>7101291</v>
+        <v>7101092</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,6 +758,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -761,21 +770,21 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133355234</v>
+        <v>133799243</v>
       </c>
       <c r="B3" t="n">
-        <v>84194</v>
+        <v>84209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -798,22 +807,33 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mariebäcken, Ång</t>
+          <t>Längs Stig Norr om Mariebäck NR, Mariebäcksnäset, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>704260</v>
+        <v>704292</v>
       </c>
       <c r="R3" t="n">
-        <v>7101092</v>
+        <v>7101077</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +857,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Brant sluttning ovan skogsstig</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -858,22 +883,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ernie Haglund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Ernie Haglund, Jörgen Sjögren, Albin Larsson Ekström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133210683</v>
+        <v>133210685</v>
       </c>
       <c r="B4" t="n">
-        <v>58349</v>
+        <v>80382</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,13 +930,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>704306</v>
+        <v>704309</v>
       </c>
       <c r="R4" t="n">
-        <v>7101057</v>
+        <v>7101053</v>
       </c>
       <c r="S4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -940,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -950,7 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133210685</v>
+        <v>133210683</v>
       </c>
       <c r="B5" t="n">
-        <v>80367</v>
+        <v>58349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -988,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1012,13 +1037,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>704309</v>
+        <v>704306</v>
       </c>
       <c r="R5" t="n">
-        <v>7101053</v>
+        <v>7101057</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1047,7 +1072,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1057,7 +1082,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,124 +1106,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>133799243</v>
-      </c>
-      <c r="B6" t="n">
-        <v>84202</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1445</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Bombmurkla</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Sarcosoma globosum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Längs Stig Norr om Mariebäck NR, Mariebäcksnäset, Ång</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>704292</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7101077</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Brant sluttning ovan skogsstig</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Ernie Haglund</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Ernie Haglund, Jörgen Sjögren, Albin Larsson Ekström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
